--- a/8. 과거차 이력/WR_과거차이력_v1.0_260414.xlsx
+++ b/8. 과거차 이력/WR_과거차이력_v1.0_260414.xlsx
@@ -290,11 +290,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>WRS-260227-001</t>
+  </si>
+  <si>
     <t>QV 100일 작전 기간에 따른, 리워크 사용품 공급 불가</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>WRS-260227-001</t>
   </si>
 </sst>
 </file>
@@ -1172,10 +1172,10 @@
     <col min="4" max="4" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="40" style="2" customWidth="1"/>
-    <col min="8" max="8" width="59.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="56.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="57.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="51.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="51.5703125" style="2" customWidth="1"/>
     <col min="11" max="11" width="46.5703125" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="51.7109375" style="2" customWidth="1"/>
@@ -1538,13 +1538,13 @@
         <v>67</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>58</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
